--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1358"/>
+  <dimension ref="A1:C1367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20788,6 +20788,141 @@
         <v>37.38</v>
       </c>
     </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>3265</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>175.7</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>8093</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>54030</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>9209</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1367"/>
+  <dimension ref="A1:C1376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20923,6 +20923,141 @@
         <v>40.1</v>
       </c>
     </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>3325</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>176.5</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>8224</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>50510</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>8708</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1376"/>
+  <dimension ref="A1:C1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21058,6 +21058,141 @@
         <v>40.1</v>
       </c>
     </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>178.3</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>50590</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>8714</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>40.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1385"/>
+  <dimension ref="A1:C1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21193,6 +21193,141 @@
         <v>40.1</v>
       </c>
     </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>178.3</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>4991</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>50590</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>8714</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>36.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1394"/>
+  <dimension ref="A1:C1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21328,6 +21328,141 @@
         <v>36.74</v>
       </c>
     </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>8173</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>51970</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>9294</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>36.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1403"/>
+  <dimension ref="A1:C1412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21463,6 +21463,141 @@
         <v>36.74</v>
       </c>
     </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>51750</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>9197</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>36.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1412"/>
+  <dimension ref="A1:C1421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21598,6 +21598,141 @@
         <v>36.74</v>
       </c>
     </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>8118</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>51750</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>9197</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>35.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1421"/>
+  <dimension ref="A1:C1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21733,6 +21733,141 @@
         <v>35.64</v>
       </c>
     </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>3285</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>176.8</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>4968</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>8131</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>9157</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>49690</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>35.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1430"/>
+  <dimension ref="A1:C1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21868,6 +21868,141 @@
         <v>35.64</v>
       </c>
     </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>9364</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>50780</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>35.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1439"/>
+  <dimension ref="A1:C1448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22003,6 +22003,141 @@
         <v>35.64</v>
       </c>
     </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>8126</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>9364</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>50780</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1448"/>
+  <dimension ref="A1:C1457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22138,6 +22138,141 @@
         <v>36.85</v>
       </c>
     </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>179.2</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>8455</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>49760</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>8962</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1457"/>
+  <dimension ref="A1:C1466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22273,6 +22273,141 @@
         <v>36.85</v>
       </c>
     </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>49880</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>36.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1466"/>
+  <dimension ref="A1:C1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22408,6 +22408,141 @@
         <v>36.85</v>
       </c>
     </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>8475</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>4979</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>49880</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>40.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1475"/>
+  <dimension ref="A1:C1484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22543,6 +22543,141 @@
         <v>40.35</v>
       </c>
     </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>3395</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>4944</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>51960</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>9157</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>40.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1484"/>
+  <dimension ref="A1:C1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22678,6 +22678,141 @@
         <v>40.35</v>
       </c>
     </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>40.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1493"/>
+  <dimension ref="A1:C1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22813,6 +22813,141 @@
         <v>40.35</v>
       </c>
     </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1502"/>
+  <dimension ref="A1:C1511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22948,6 +22948,141 @@
         <v>39.09</v>
       </c>
     </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1511"/>
+  <dimension ref="A1:C1520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23083,6 +23083,141 @@
         <v>39.09</v>
       </c>
     </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1520"/>
+  <dimension ref="A1:C1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23218,6 +23218,141 @@
         <v>39.09</v>
       </c>
     </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1529"/>
+  <dimension ref="A1:C1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23353,6 +23353,141 @@
         <v>41.2</v>
       </c>
     </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1538"/>
+  <dimension ref="A1:C1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23488,6 +23488,141 @@
         <v>41.2</v>
       </c>
     </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1547"/>
+  <dimension ref="A1:C1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23623,6 +23623,141 @@
         <v>41.2</v>
       </c>
     </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>41.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1556"/>
+  <dimension ref="A1:C1565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23758,6 +23758,141 @@
         <v>41.54</v>
       </c>
     </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>4947</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>54570</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>9375</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>41.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1565"/>
+  <dimension ref="A1:C1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23893,6 +23893,141 @@
         <v>41.44</v>
       </c>
     </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>175.3</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>2971.5</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>8235</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>4863</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>54980</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>9268</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>41.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1574"/>
+  <dimension ref="A1:C1583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24028,6 +24028,141 @@
         <v>41.44</v>
       </c>
     </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>41.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1583"/>
+  <dimension ref="A1:C1592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24163,6 +24163,141 @@
         <v>41.44</v>
       </c>
     </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1592"/>
+  <dimension ref="A1:C1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24298,6 +24298,141 @@
         <v>41.51</v>
       </c>
     </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>174.9</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>8196</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>54580</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1601" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1601"/>
+  <dimension ref="A1:C1610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24433,6 +24433,141 @@
         <v>41.51</v>
       </c>
     </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1602" t="n">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1603" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1604" t="n">
+        <v>175.7</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1605" t="n">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>8181</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>4857</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>55880</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>9301</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1610"/>
+  <dimension ref="A1:C1619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24568,6 +24568,141 @@
         <v>41.51</v>
       </c>
     </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>2989.5</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>55780</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
+        <v>41.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1619"/>
+  <dimension ref="A1:C1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24703,6 +24703,141 @@
         <v>41.51</v>
       </c>
     </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>2989.5</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>55780</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>43.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1628"/>
+  <dimension ref="A1:C1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24838,6 +24838,141 @@
         <v>43.26</v>
       </c>
     </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>175.5</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>3016</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>8065</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>54480</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>9153</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>43.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1637"/>
+  <dimension ref="A1:C1646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24973,6 +24973,141 @@
         <v>43.26</v>
       </c>
     </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>174.7</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>2986.5</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>53340</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>9093</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>43.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1646"/>
+  <dimension ref="A1:C1655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25108,6 +25108,141 @@
         <v>43.26</v>
       </c>
     </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>2936.5</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>9048</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>17780</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1655"/>
+  <dimension ref="A1:C1664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25243,6 +25243,141 @@
         <v>41.78</v>
       </c>
     </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>8968</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>17655</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1664"/>
+  <dimension ref="A1:C1673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25378,6 +25378,141 @@
         <v>41.78</v>
       </c>
     </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>171.3</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>2881.5</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>9117</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>17880</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1673"/>
+  <dimension ref="A1:C1682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25513,6 +25513,141 @@
         <v>41.78</v>
       </c>
     </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>171.3</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>2881.5</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>9117</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>17880</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>41.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1682"/>
+  <dimension ref="A1:C1691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25648,6 +25648,141 @@
         <v>41.02</v>
       </c>
     </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>170.6</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>9450</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>18265</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>41.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1691"/>
+  <dimension ref="A1:C1700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25783,6 +25783,141 @@
         <v>41.02</v>
       </c>
     </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>9324</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>18095</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>41.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1700"/>
+  <dimension ref="A1:C1709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25918,6 +25918,141 @@
         <v>41.02</v>
       </c>
     </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>7944</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>9324</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>18095</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1709"/>
+  <dimension ref="A1:C1718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26053,6 +26053,141 @@
         <v>41.07</v>
       </c>
     </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>170.7</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1713" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1714" t="n">
+        <v>10185</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1715" t="n">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1716" t="n">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1717" t="n">
+        <v>18855</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1718" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1718"/>
+  <dimension ref="A1:C1727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26188,6 +26188,141 @@
         <v>41.07</v>
       </c>
     </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1719" t="n">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1720" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1721" t="n">
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1722" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1723" t="n">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1724" t="n">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1725" t="n">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1726" t="n">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1727" t="n">
+        <v>41.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1727"/>
+  <dimension ref="A1:C1736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26323,6 +26323,141 @@
         <v>41.07</v>
       </c>
     </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1728" t="n">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1729" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1730" t="n">
+        <v>170.3</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1731" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1732" t="n">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1733" t="n">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1734" t="n">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1735" t="n">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1736" t="n">
+        <v>41.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1736"/>
+  <dimension ref="A1:C1745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26458,6 +26458,141 @@
         <v>41.92</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1737" t="n">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1738" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1739" t="n">
+        <v>169.3</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1740" t="n">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1741" t="n">
+        <v>9871</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1742" t="n">
+        <v>7832</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1743" t="n">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1744" t="n">
+        <v>19170</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1745" t="n">
+        <v>41.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1745"/>
+  <dimension ref="A1:C1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26593,6 +26593,141 @@
         <v>41.92</v>
       </c>
     </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1746" t="n">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1747" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1748" t="n">
+        <v>169.9</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1749" t="n">
+        <v>10095</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1750" t="n">
+        <v>2856.5</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1751" t="n">
+        <v>7849</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1752" t="n">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1753" t="n">
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1754" t="n">
+        <v>41.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1754"/>
+  <dimension ref="A1:C1763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26728,6 +26728,141 @@
         <v>41.92</v>
       </c>
     </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1755" t="n">
+        <v>3370</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1756" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1757" t="n">
+        <v>169.9</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1758" t="n">
+        <v>10095</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1759" t="n">
+        <v>2856.5</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1760" t="n">
+        <v>7849</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1761" t="n">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1762" t="n">
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1763" t="n">
+        <v>43.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1763"/>
+  <dimension ref="A1:C1772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26863,6 +26863,141 @@
         <v>43.69</v>
       </c>
     </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1764" t="n">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1765" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1766" t="n">
+        <v>10685</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1767" t="n">
+        <v>167.3</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1768" t="n">
+        <v>2889.5</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1769" t="n">
+        <v>7853</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1770" t="n">
+        <v>4691</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1771" t="n">
+        <v>19395</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1772" t="n">
+        <v>43.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1772"/>
+  <dimension ref="A1:C1781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26998,6 +26998,141 @@
         <v>43.69</v>
       </c>
     </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1773" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1774" t="n">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1775" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1776" t="n">
+        <v>10490</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1777" t="n">
+        <v>2893.5</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1778" t="n">
+        <v>4709</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1779" t="n">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1780" t="n">
+        <v>19120</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1781" t="n">
+        <v>43.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1781"/>
+  <dimension ref="A1:C1790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27133,6 +27133,141 @@
         <v>43.69</v>
       </c>
     </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1782" t="n">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1783" t="n">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1784" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1785" t="n">
+        <v>10490</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1786" t="n">
+        <v>2893.5</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1787" t="n">
+        <v>4709</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1788" t="n">
+        <v>7742</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1789" t="n">
+        <v>19120</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1790" t="n">
+        <v>43.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1790"/>
+  <dimension ref="A1:C1799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27268,6 +27268,141 @@
         <v>43.19</v>
       </c>
     </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1791" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1792" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1793" t="n">
+        <v>169.8</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1794" t="n">
+        <v>10635</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1795" t="n">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1796" t="n">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1797" t="n">
+        <v>7805</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1798" t="n">
+        <v>18535</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1799" t="n">
+        <v>43.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1799"/>
+  <dimension ref="A1:C1808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27403,6 +27403,141 @@
         <v>43.19</v>
       </c>
     </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1800" t="n">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1801" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1802" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1803" t="n">
+        <v>170.1</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1804" t="n">
+        <v>2930.5</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1805" t="n">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1806" t="n">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1807" t="n">
+        <v>18735</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1808" t="n">
+        <v>43.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1808"/>
+  <dimension ref="A1:C1817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27538,6 +27538,141 @@
         <v>43.19</v>
       </c>
     </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1809" t="n">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1810" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1811" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1812" t="n">
+        <v>170.1</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1813" t="n">
+        <v>2930.5</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1814" t="n">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1815" t="n">
+        <v>7815</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1816" t="n">
+        <v>18735</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1817" t="n">
+        <v>43.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1817"/>
+  <dimension ref="A1:C1826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27673,6 +27673,141 @@
         <v>43.46</v>
       </c>
     </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1818" t="n">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1819" t="n">
+        <v>11645</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1820" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1821" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1822" t="n">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1823" t="n">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1824" t="n">
+        <v>7795</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1825" t="n">
+        <v>17975</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1826" t="n">
+        <v>43.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1826"/>
+  <dimension ref="A1:C1835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27808,6 +27808,141 @@
         <v>43.46</v>
       </c>
     </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1827" t="n">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1828" t="n">
+        <v>11460</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1829" t="n">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1830" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1831" t="n">
+        <v>2900.5</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1832" t="n">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1833" t="n">
+        <v>7775</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1834" t="n">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1835" t="n">
+        <v>43.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1835"/>
+  <dimension ref="A1:C1844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27943,6 +27943,141 @@
         <v>43.46</v>
       </c>
     </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1836" t="n">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1837" t="n">
+        <v>11460</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1838" t="n">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1839" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1840" t="n">
+        <v>2900.5</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1841" t="n">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1842" t="n">
+        <v>7775</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1843" t="n">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1844" t="n">
+        <v>44.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1844"/>
+  <dimension ref="A1:C1853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28078,6 +28078,141 @@
         <v>44.94</v>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1845" t="n">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1846" t="n">
+        <v>11405</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1847" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1848" t="n">
+        <v>170.1</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1849" t="n">
+        <v>2898.5</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1850" t="n">
+        <v>7789</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1851" t="n">
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1852" t="n">
+        <v>18450</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1853" t="n">
+        <v>44.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1853"/>
+  <dimension ref="A1:C1862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28213,6 +28213,141 @@
         <v>44.94</v>
       </c>
     </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1855" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1856" t="n">
+        <v>10955</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1857" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1858" t="n">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1859" t="n">
+        <v>7851</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1860" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1861" t="n">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1862" t="n">
+        <v>44.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1862"/>
+  <dimension ref="A1:C1871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28348,6 +28348,141 @@
         <v>44.94</v>
       </c>
     </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1863" t="n">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1864" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1865" t="n">
+        <v>10955</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1866" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1867" t="n">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1868" t="n">
+        <v>7851</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1869" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1870" t="n">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1871" t="n">
+        <v>42.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1871"/>
+  <dimension ref="A1:C1880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28483,6 +28483,141 @@
         <v>42.77</v>
       </c>
     </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1872" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1873" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1874" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1875" t="n">
+        <v>10850</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1876" t="n">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1877" t="n">
+        <v>8113</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1878" t="n">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1879" t="n">
+        <v>17220</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1880" t="n">
+        <v>42.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1880"/>
+  <dimension ref="A1:C1889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28618,6 +28618,141 @@
         <v>42.77</v>
       </c>
     </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1881" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1882" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1883" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1884" t="n">
+        <v>172.9</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1885" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1886" t="n">
+        <v>8146</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1887" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1888" t="n">
+        <v>17505</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1889" t="n">
+        <v>42.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1889"/>
+  <dimension ref="A1:C1898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28753,6 +28753,141 @@
         <v>42.77</v>
       </c>
     </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1890" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1891" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1892" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1893" t="n">
+        <v>172.9</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1894" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1895" t="n">
+        <v>8146</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1896" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1897" t="n">
+        <v>17505</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1898" t="n">
+        <v>41.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1898"/>
+  <dimension ref="A1:C1907"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28888,6 +28888,141 @@
         <v>41.86</v>
       </c>
     </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1899" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1900" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1901" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1902" t="n">
+        <v>172.9</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1903" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1904" t="n">
+        <v>8146</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1905" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1906" t="n">
+        <v>17505</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1907" t="n">
+        <v>41.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1907"/>
+  <dimension ref="A1:C1916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29023,6 +29023,141 @@
         <v>41.86</v>
       </c>
     </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1908" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1909" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1910" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1911" t="n">
+        <v>172.9</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1912" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1913" t="n">
+        <v>8146</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1914" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1915" t="n">
+        <v>17505</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1916" t="n">
+        <v>41.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1916"/>
+  <dimension ref="A1:C1925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29158,6 +29158,141 @@
         <v>41.86</v>
       </c>
     </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1917" t="n">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1918" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1919" t="n">
+        <v>11135</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1920" t="n">
+        <v>172.9</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1921" t="n">
+        <v>2910.5</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1922" t="n">
+        <v>8146</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1923" t="n">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1924" t="n">
+        <v>17505</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1925" t="n">
+        <v>39.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1925"/>
+  <dimension ref="A1:C1934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29293,6 +29293,141 @@
         <v>39.98</v>
       </c>
     </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1926" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1927" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1928" t="n">
+        <v>173.2</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1929" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1930" t="n">
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1931" t="n">
+        <v>10115</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1932" t="n">
+        <v>4633</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1933" t="n">
+        <v>15330</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1934" t="n">
+        <v>39.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1934"/>
+  <dimension ref="A1:C1943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29428,6 +29428,141 @@
         <v>39.98</v>
       </c>
     </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1935" t="n">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1936" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1937" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1938" t="n">
+        <v>10590</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1939" t="n">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1940" t="n">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1941" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1942" t="n">
+        <v>15180</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1943" t="n">
+        <v>39.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1943"/>
+  <dimension ref="A1:C1952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29563,6 +29563,141 @@
         <v>39.98</v>
       </c>
     </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1944" t="n">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1945" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1946" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1947" t="n">
+        <v>10590</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1948" t="n">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1949" t="n">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1950" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1951" t="n">
+        <v>15180</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1952" t="n">
+        <v>39.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1952"/>
+  <dimension ref="A1:C1961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29698,6 +29698,141 @@
         <v>39.07</v>
       </c>
     </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1953" t="n">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1954" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1955" t="n">
+        <v>11410</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1956" t="n">
+        <v>172.2</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1957" t="n">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1958" t="n">
+        <v>8268</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1959" t="n">
+        <v>4705</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1960" t="n">
+        <v>14910</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1961" t="n">
+        <v>39.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1961"/>
+  <dimension ref="A1:C1970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29833,6 +29833,141 @@
         <v>39.07</v>
       </c>
     </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1962" t="n">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1963" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1964" t="n">
+        <v>10970</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1965" t="n">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1966" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1967" t="n">
+        <v>8278</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1968" t="n">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1969" t="n">
+        <v>14690</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1970" t="n">
+        <v>39.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1970"/>
+  <dimension ref="A1:C1979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29968,6 +29968,141 @@
         <v>39.07</v>
       </c>
     </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1972" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1973" t="n">
+        <v>10970</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1974" t="n">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1975" t="n">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>8278</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>14690</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>35.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1979"/>
+  <dimension ref="A1:C1988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30103,6 +30103,141 @@
         <v>35.78</v>
       </c>
     </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>8305</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>10105</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>4641</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>13040</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>35.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1988"/>
+  <dimension ref="A1:C1997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30238,6 +30238,141 @@
         <v>35.78</v>
       </c>
     </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>8228</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>9864</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>12880</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>35.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1997"/>
+  <dimension ref="A1:C2006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30373,6 +30373,141 @@
         <v>35.78</v>
       </c>
     </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>8228</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>9864</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>12880</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2006"/>
+  <dimension ref="A1:C2015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30508,6 +30508,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>174.2</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2010" t="n">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2011" t="n">
+        <v>8535</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2012" t="n">
+        <v>9962</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2013" t="n">
+        <v>4737</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2014" t="n">
+        <v>13310</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2015" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2015"/>
+  <dimension ref="A1:C2024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30643,6 +30643,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2016" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2017" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2018" t="n">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2019" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2020" t="n">
+        <v>8479</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2021" t="n">
+        <v>10070</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2022" t="n">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2023" t="n">
+        <v>13375</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2024" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2024"/>
+  <dimension ref="A1:C2033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30778,6 +30778,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2025" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2026" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2027" t="n">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2028" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2029" t="n">
+        <v>8479</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2030" t="n">
+        <v>10070</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2031" t="n">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2032" t="n">
+        <v>13375</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2033" t="n">
+        <v>31.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2033"/>
+  <dimension ref="A1:C2042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30913,6 +30913,141 @@
         <v>31.63</v>
       </c>
     </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2034" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2035" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2036" t="n">
+        <v>176.4</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2037" t="n">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2038" t="n">
+        <v>8555</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2039" t="n">
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2040" t="n">
+        <v>9384</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2041" t="n">
+        <v>13450</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2042" t="n">
+        <v>31.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2042"/>
+  <dimension ref="A1:C2051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31048,6 +31048,141 @@
         <v>31.63</v>
       </c>
     </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2043" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2044" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2045" t="n">
+        <v>175.1</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2046" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2047" t="n">
+        <v>8541</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2048" t="n">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2049" t="n">
+        <v>9582</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2050" t="n">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2051" t="n">
+        <v>31.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2051"/>
+  <dimension ref="A1:C2060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31183,6 +31183,141 @@
         <v>31.63</v>
       </c>
     </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2052" t="n">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2053" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2054" t="n">
+        <v>175.1</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2055" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2056" t="n">
+        <v>8541</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2057" t="n">
+        <v>4761</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2058" t="n">
+        <v>9582</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2059" t="n">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2060" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2060"/>
+  <dimension ref="A1:C2069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31318,6 +31318,141 @@
         <v>32.1</v>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2061" t="n">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2062" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2063" t="n">
+        <v>175.7</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2064" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2065" t="n">
+        <v>8630</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2066" t="n">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2067" t="n">
+        <v>9434</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2068" t="n">
+        <v>13385</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2069" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2069"/>
+  <dimension ref="A1:C2078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31453,6 +31453,141 @@
         <v>32.1</v>
       </c>
     </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2070" t="n">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2071" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2072" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2073" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2074" t="n">
+        <v>8680</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2075" t="n">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2076" t="n">
+        <v>9095</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2077" t="n">
+        <v>13140</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2078" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2078"/>
+  <dimension ref="A1:C2087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31588,6 +31588,141 @@
         <v>32.1</v>
       </c>
     </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2079" t="n">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2080" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2081" t="n">
+        <v>177.1</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2082" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2083" t="n">
+        <v>8680</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2084" t="n">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2085" t="n">
+        <v>9095</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2086" t="n">
+        <v>13140</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2087" t="n">
+        <v>32.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2087"/>
+  <dimension ref="A1:C2096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31723,6 +31723,141 @@
         <v>32.47</v>
       </c>
     </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2088" t="n">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2089" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2090" t="n">
+        <v>175.6</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2091" t="n">
+        <v>8714</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2092" t="n">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2093" t="n">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2094" t="n">
+        <v>9468</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2095" t="n">
+        <v>13560</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2096" t="n">
+        <v>32.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2096"/>
+  <dimension ref="A1:C2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31858,6 +31858,141 @@
         <v>32.47</v>
       </c>
     </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2097" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2098" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2099" t="n">
+        <v>176.2</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2100" t="n">
+        <v>8715</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2101" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2102" t="n">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2103" t="n">
+        <v>9253</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2104" t="n">
+        <v>13510</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2105" t="n">
+        <v>32.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2105"/>
+  <dimension ref="A1:C2114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31993,6 +31993,141 @@
         <v>32.47</v>
       </c>
     </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2106" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2107" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2108" t="n">
+        <v>176.2</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2109" t="n">
+        <v>8715</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2110" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2111" t="n">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2112" t="n">
+        <v>9253</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2113" t="n">
+        <v>13510</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2114" t="n">
+        <v>35.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2114"/>
+  <dimension ref="A1:C2123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32128,6 +32128,141 @@
         <v>35.57</v>
       </c>
     </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2115" t="n">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2116" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2117" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2118" t="n">
+        <v>8776</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2119" t="n">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2120" t="n">
+        <v>4823</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2121" t="n">
+        <v>8955</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2122" t="n">
+        <v>13060</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2123" t="n">
+        <v>35.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2123"/>
+  <dimension ref="A1:C2132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32263,6 +32263,141 @@
         <v>35.57</v>
       </c>
     </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2124" t="n">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2125" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2126" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2127" t="n">
+        <v>8699</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2128" t="n">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2129" t="n">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2130" t="n">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2131" t="n">
+        <v>12595</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2132" t="n">
+        <v>35.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2132"/>
+  <dimension ref="A1:C2141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32398,6 +32398,141 @@
         <v>35.57</v>
       </c>
     </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2133" t="n">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2134" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2135" t="n">
+        <v>178.1</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2136" t="n">
+        <v>8699</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2137" t="n">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2138" t="n">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2139" t="n">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2140" t="n">
+        <v>12595</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2141" t="n">
+        <v>33.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2141"/>
+  <dimension ref="A1:C2150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32533,6 +32533,141 @@
         <v>33.72</v>
       </c>
     </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2142" t="n">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2143" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2144" t="n">
+        <v>178.3</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2145" t="n">
+        <v>3095</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2146" t="n">
+        <v>8615</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2147" t="n">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2148" t="n">
+        <v>8039</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2149" t="n">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2150" t="n">
+        <v>33.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2150"/>
+  <dimension ref="A1:C2159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32668,6 +32668,141 @@
         <v>33.72</v>
       </c>
     </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2151" t="n">
+        <v>3665</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2152" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2153" t="n">
+        <v>174.8</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2154" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2155" t="n">
+        <v>8539</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2156" t="n">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2157" t="n">
+        <v>8364</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2158" t="n">
+        <v>12755</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2159" t="n">
+        <v>33.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2159"/>
+  <dimension ref="A1:C2168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32803,6 +32803,141 @@
         <v>33.72</v>
       </c>
     </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2160" t="n">
+        <v>3665</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2161" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2162" t="n">
+        <v>174.8</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2163" t="n">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2164" t="n">
+        <v>8539</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2165" t="n">
+        <v>4715</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2166" t="n">
+        <v>8364</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2167" t="n">
+        <v>12755</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2168" t="n">
+        <v>32.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2168"/>
+  <dimension ref="A1:C2177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32938,6 +32938,141 @@
         <v>32.94</v>
       </c>
     </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2169" t="n">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2170" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2171" t="n">
+        <v>177.5</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2172" t="n">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2173" t="n">
+        <v>8584</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2174" t="n">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2175" t="n">
+        <v>8478</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2176" t="n">
+        <v>12380</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2177" t="n">
+        <v>32.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2177"/>
+  <dimension ref="A1:C2186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33073,6 +33073,141 @@
         <v>32.94</v>
       </c>
     </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2178" t="n">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2179" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2180" t="n">
+        <v>176.4</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2181" t="n">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2182" t="n">
+        <v>8576</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2183" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2184" t="n">
+        <v>8572</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2185" t="n">
+        <v>12550</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2186" t="n">
+        <v>32.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2186"/>
+  <dimension ref="A1:C2195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33208,6 +33208,141 @@
         <v>32.94</v>
       </c>
     </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2187" t="n">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2188" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2189" t="n">
+        <v>176.4</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2190" t="n">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2191" t="n">
+        <v>8576</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2192" t="n">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2193" t="n">
+        <v>8572</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2194" t="n">
+        <v>12550</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2195" t="n">
+        <v>32.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2195"/>
+  <dimension ref="A1:C2204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33343,6 +33343,141 @@
         <v>32.69</v>
       </c>
     </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2196" t="n">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2197" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2198" t="n">
+        <v>175.1</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2199" t="n">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2200" t="n">
+        <v>8501</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2201" t="n">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2202" t="n">
+        <v>8736</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2203" t="n">
+        <v>12570</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2204" t="n">
+        <v>32.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2204"/>
+  <dimension ref="A1:C2213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33478,6 +33478,141 @@
         <v>32.69</v>
       </c>
     </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2205" t="n">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2206" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2207" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2208" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2209" t="n">
+        <v>8453</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2210" t="n">
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2211" t="n">
+        <v>8587</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2212" t="n">
+        <v>12605</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2213" t="n">
+        <v>32.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2213"/>
+  <dimension ref="A1:C2222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33613,6 +33613,141 @@
         <v>32.69</v>
       </c>
     </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2214" t="n">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2215" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2216" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2217" t="n">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2218" t="n">
+        <v>8453</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2219" t="n">
+        <v>4936</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2220" t="n">
+        <v>8587</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2221" t="n">
+        <v>12605</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2222" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2222"/>
+  <dimension ref="A1:C2231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33748,6 +33748,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2223" t="n">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2224" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2225" t="n">
+        <v>172.1</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2226" t="n">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2227" t="n">
+        <v>8263</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2228" t="n">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2229" t="n">
+        <v>9309</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2230" t="n">
+        <v>14240</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2231" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2231"/>
+  <dimension ref="A1:C2240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33883,6 +33883,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2232" t="n">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2233" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2234" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2235" t="n">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2236" t="n">
+        <v>8311</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2237" t="n">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2238" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2239" t="n">
+        <v>14340</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2240" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2240"/>
+  <dimension ref="A1:C2249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34018,6 +34018,141 @@
         <v>35.09</v>
       </c>
     </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2241" t="n">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2242" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2243" t="n">
+        <v>171.9</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2244" t="n">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2245" t="n">
+        <v>8311</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2246" t="n">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2247" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2248" t="n">
+        <v>14340</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2249" t="n">
+        <v>35.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2249"/>
+  <dimension ref="A1:C2258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34153,6 +34153,141 @@
         <v>35.81</v>
       </c>
     </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2250" t="n">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2251" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2252" t="n">
+        <v>172.3</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2253" t="n">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2254" t="n">
+        <v>8259</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2255" t="n">
+        <v>4867</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2256" t="n">
+        <v>8914</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2257" t="n">
+        <v>14850</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2258" t="n">
+        <v>35.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2258"/>
+  <dimension ref="A1:C2267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34288,6 +34288,141 @@
         <v>35.81</v>
       </c>
     </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2259" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2260" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2261" t="n">
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2262" t="n">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2263" t="n">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2264" t="n">
+        <v>8158</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2265" t="n">
+        <v>9231</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2266" t="n">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2267" t="n">
+        <v>35.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2267"/>
+  <dimension ref="A1:C2276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34423,6 +34423,141 @@
         <v>35.81</v>
       </c>
     </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2268" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2269" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2270" t="n">
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2271" t="n">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2272" t="n">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2273" t="n">
+        <v>8158</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2274" t="n">
+        <v>9231</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2275" t="n">
+        <v>14505</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2276" t="n">
+        <v>34.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2276"/>
+  <dimension ref="A1:C2285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34558,6 +34558,141 @@
         <v>34.43</v>
       </c>
     </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2277" t="n">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2278" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2279" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2280" t="n">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2281" t="n">
+        <v>8262</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2282" t="n">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2283" t="n">
+        <v>8442</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2284" t="n">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2285" t="n">
+        <v>34.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/price_history.xlsx
+++ b/price_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2285"/>
+  <dimension ref="A1:C2294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34693,6 +34693,141 @@
         <v>34.43</v>
       </c>
     </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>4431.T</t>
+        </is>
+      </c>
+      <c r="C2286" t="n">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="C2287" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="C2288" t="n">
+        <v>173.3</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="C2289" t="n">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="C2290" t="n">
+        <v>8289</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="C2291" t="n">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="C2292" t="n">
+        <v>8553</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="C2293" t="n">
+        <v>13470</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C2294" t="n">
+        <v>34.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
